--- a/template/Template.xlsx
+++ b/template/Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724696F-5F37-43BD-A50C-E6693CEFF4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD927D2-72FE-4BB6-8732-BC512D912549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +403,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF305496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,7 +532,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -594,9 +600,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -608,6 +611,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1062,31 +1072,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="32" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="31" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="32" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1100,7 +1111,7 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="24" t="s">
@@ -1129,529 +1140,529 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="32">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="32">
         <f>'a. Access Management'!F1</f>
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="32">
         <f t="shared" ref="D7:D16" si="0">C7-I7</f>
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="32">
         <f>COUNTIF('a. Access Management'!L:L,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="32">
         <f>COUNTIF('a. Access Management'!L:L,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="32">
         <f>COUNTIF('a. Access Management'!L:L,"Pending")</f>
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="32">
         <f>COUNTIF('a. Access Management'!L:L,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="32">
         <f>COUNTIF('a. Access Management'!L:L,"Not test")</f>
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="32">
         <f>COUNTIFS('a. Access Management'!B:B,"TC-*",'a. Access Management'!L:L,"")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="33" t="str">
         <f t="shared" ref="K7:K17" si="1">IF(D7=0,"N/A",(E7+F7+H7)/D7)</f>
         <v>N/A</v>
       </c>
-      <c r="L7" s="26" t="str">
+      <c r="L7" s="33" t="str">
         <f t="shared" ref="L7:L17" si="2">IF(D7=0,"N/A",E7/D7)</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="32">
         <v>5</v>
       </c>
-      <c r="C8" t="e">
+      <c r="C8" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D8" t="e">
+      <c r="D8" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E8" t="e">
+      <c r="E8" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F8" t="e">
+      <c r="F8" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G8" t="e">
+      <c r="G8" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H8" t="e">
+      <c r="H8" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I8" t="e">
+      <c r="I8" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J8" t="e">
+      <c r="J8" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K8" s="26" t="e">
+      <c r="K8" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L8" s="26" t="e">
+      <c r="L8" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="32">
         <v>7</v>
       </c>
-      <c r="C9" t="e">
+      <c r="C9" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D9" t="e">
+      <c r="D9" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E9" t="e">
+      <c r="E9" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F9" t="e">
+      <c r="F9" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G9" t="e">
+      <c r="G9" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H9" t="e">
+      <c r="H9" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I9" t="e">
+      <c r="I9" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J9" t="e">
+      <c r="J9" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K9" s="26" t="e">
+      <c r="K9" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L9" s="26" t="e">
+      <c r="L9" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="32">
         <v>7</v>
       </c>
-      <c r="C10" t="e">
+      <c r="C10" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D10" t="e">
+      <c r="D10" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E10" t="e">
+      <c r="E10" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F10" t="e">
+      <c r="F10" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G10" t="e">
+      <c r="G10" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H10" t="e">
+      <c r="H10" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I10" t="e">
+      <c r="I10" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J10" t="e">
+      <c r="J10" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K10" s="26" t="e">
+      <c r="K10" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L10" s="26" t="e">
+      <c r="L10" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="32">
         <v>6</v>
       </c>
-      <c r="C11" t="e">
+      <c r="C11" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D11" t="e">
+      <c r="D11" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E11" t="e">
+      <c r="E11" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F11" t="e">
+      <c r="F11" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G11" t="e">
+      <c r="G11" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H11" t="e">
+      <c r="H11" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I11" t="e">
+      <c r="I11" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J11" t="e">
+      <c r="J11" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K11" s="26" t="e">
+      <c r="K11" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L11" s="26" t="e">
+      <c r="L11" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="32">
         <v>13</v>
       </c>
-      <c r="C12" t="e">
+      <c r="C12" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D12" t="e">
+      <c r="D12" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E12" t="e">
+      <c r="E12" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F12" t="e">
+      <c r="F12" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G12" t="e">
+      <c r="G12" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" t="e">
+      <c r="H12" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" t="e">
+      <c r="I12" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J12" t="e">
+      <c r="J12" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K12" s="26" t="e">
+      <c r="K12" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L12" s="26" t="e">
+      <c r="L12" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="32">
         <v>5</v>
       </c>
-      <c r="C13" t="e">
+      <c r="C13" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D13" t="e">
+      <c r="D13" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E13" t="e">
+      <c r="E13" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F13" t="e">
+      <c r="F13" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G13" t="e">
+      <c r="G13" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H13" t="e">
+      <c r="H13" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I13" t="e">
+      <c r="I13" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J13" t="e">
+      <c r="J13" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K13" s="26" t="e">
+      <c r="K13" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L13" s="26" t="e">
+      <c r="L13" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="32">
         <v>5</v>
       </c>
-      <c r="C14" t="e">
+      <c r="C14" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D14" t="e">
+      <c r="D14" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E14" t="e">
+      <c r="E14" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F14" t="e">
+      <c r="F14" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G14" t="e">
+      <c r="G14" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H14" t="e">
+      <c r="H14" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I14" t="e">
+      <c r="I14" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J14" t="e">
+      <c r="J14" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K14" s="26" t="e">
+      <c r="K14" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L14" s="26" t="e">
+      <c r="L14" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="32">
         <v>11</v>
       </c>
-      <c r="C15" t="e">
+      <c r="C15" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D15" t="e">
+      <c r="D15" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E15" t="e">
+      <c r="E15" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F15" t="e">
+      <c r="F15" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G15" t="e">
+      <c r="G15" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" t="e">
+      <c r="H15" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I15" t="e">
+      <c r="I15" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J15" t="e">
+      <c r="J15" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K15" s="26" t="e">
+      <c r="K15" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L15" s="26" t="e">
+      <c r="L15" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="32">
         <v>9</v>
       </c>
-      <c r="C16" t="e">
+      <c r="C16" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D16" t="e">
+      <c r="D16" s="32" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="E16" t="e">
+      <c r="E16" s="32" t="e">
         <f>COUNTIF(#REF!,"Passed")</f>
         <v>#REF!</v>
       </c>
-      <c r="F16" t="e">
+      <c r="F16" s="32" t="e">
         <f>COUNTIF(#REF!,"Failed")</f>
         <v>#REF!</v>
       </c>
-      <c r="G16" t="e">
+      <c r="G16" s="32" t="e">
         <f>COUNTIF(#REF!,"Pending")</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" t="e">
+      <c r="H16" s="32" t="e">
         <f>COUNTIF(#REF!,"Blocked")</f>
         <v>#REF!</v>
       </c>
-      <c r="I16" t="e">
+      <c r="I16" s="32" t="e">
         <f>COUNTIF(#REF!,"Not test")</f>
         <v>#REF!</v>
       </c>
-      <c r="J16" t="e">
+      <c r="J16" s="32" t="e">
         <f>COUNTIFS(#REF!,"TC-*",#REF!,"")</f>
         <v>#REF!</v>
       </c>
-      <c r="K16" s="26" t="e">
+      <c r="K16" s="33" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L16" s="26" t="e">
+      <c r="L16" s="33" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="34">
         <v>75</v>
       </c>
-      <c r="C17" s="3" t="e">
+      <c r="C17" s="34" t="e">
         <f t="shared" ref="C17:J17" si="3">SUM(C7:C16)</f>
         <v>#REF!</v>
       </c>
-      <c r="D17" s="3" t="e">
+      <c r="D17" s="34" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="E17" s="25" t="e">
+      <c r="E17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="F17" s="25" t="e">
+      <c r="F17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="G17" s="25" t="e">
+      <c r="G17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="H17" s="25" t="e">
+      <c r="H17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="I17" s="25" t="e">
+      <c r="I17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="J17" s="25" t="e">
+      <c r="J17" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K17" s="27" t="e">
+      <c r="K17" s="36" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="L17" s="27" t="e">
+      <c r="L17" s="36" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
@@ -2032,23 +2043,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
     </row>
     <row r="11" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -2420,21 +2431,21 @@
       <c r="O32" s="16"/>
     </row>
     <row r="33" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
     </row>
     <row r="34" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
@@ -2539,21 +2550,21 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
     </row>
     <row r="41" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
@@ -2658,21 +2669,21 @@
       <c r="O46" s="5"/>
     </row>
     <row r="47" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
     </row>
     <row r="48" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
@@ -2845,21 +2856,21 @@
       <c r="O57" s="5"/>
     </row>
     <row r="58" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="31"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
-      <c r="N58" s="32"/>
-      <c r="O58" s="32"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
     </row>
     <row r="59" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
@@ -2913,21 +2924,21 @@
       <c r="O61" s="5"/>
     </row>
     <row r="62" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
-      <c r="M62" s="32"/>
-      <c r="N62" s="32"/>
-      <c r="O62" s="32"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
     </row>
     <row r="63" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
@@ -3032,21 +3043,21 @@
       <c r="O68" s="5"/>
     </row>
     <row r="69" spans="1:15" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="31"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
-      <c r="N69" s="32"/>
-      <c r="O69" s="32"/>
+      <c r="A69" s="28"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
     </row>
     <row r="70" spans="1:15" ht="75.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
@@ -3246,26 +3257,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8449ae91-dccb-4777-ab63-ca97fcf52e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="94a5f08c-f190-4aff-8e4c-063de6e29824" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010085E0FFA8BC67C04FA808A66F8AA4AC89" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fb15e306fabcad1d5449123032da1fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8449ae91-dccb-4777-ab63-ca97fcf52e1c" xmlns:ns3="94a5f08c-f190-4aff-8e4c-063de6e29824" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c9d028d14b999a0dff958b518de8b73" ns2:_="" ns3:_="">
     <xsd:import namespace="8449ae91-dccb-4777-ab63-ca97fcf52e1c"/>
@@ -3506,10 +3497,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8449ae91-dccb-4777-ab63-ca97fcf52e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="94a5f08c-f190-4aff-8e4c-063de6e29824" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1752FB0A-89A9-480D-B37A-A06BD1362BCD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{303F6E0E-D408-4CE6-9E73-CE50A90B0616}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8449ae91-dccb-4777-ab63-ca97fcf52e1c"/>
+    <ds:schemaRef ds:uri="94a5f08c-f190-4aff-8e4c-063de6e29824"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3526,20 +3548,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{303F6E0E-D408-4CE6-9E73-CE50A90B0616}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1752FB0A-89A9-480D-B37A-A06BD1362BCD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8449ae91-dccb-4777-ab63-ca97fcf52e1c"/>
-    <ds:schemaRef ds:uri="94a5f08c-f190-4aff-8e4c-063de6e29824"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>